--- a/website/public/templates/quotes-template.xlsx
+++ b/website/public/templates/quotes-template.xlsx
@@ -1,58 +1,85 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="8">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00444444"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001A7F37"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00888888"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F7FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,18 +87,132 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -396,217 +537,628 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Quotes Template — Instructions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>For importing supplier price quotes. One row = one quote.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>project_code</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>e.g. PRY001</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>entity_document_number</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Supplier's RUC or DNI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>date_received</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Description of what's being quoted</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>unit_of_measure</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>e.g. bags, m3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>unit_price</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>subtotal</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Before IGV</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>igv_amount</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Validated against subtotal × 18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Validated against subtotal + igv_amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>USD or PEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>exchange_rate</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>2.5–6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>pending, accepted, or rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>document_ref</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="24.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="17.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="23.83203125" customWidth="1"/>
-    <col min="9" max="9" width="30.83203125" customWidth="1"/>
-    <col min="10" max="10" width="24.83203125" customWidth="1"/>
-    <col min="11" max="11" width="15.83203125" customWidth="1"/>
-    <col min="12" max="12" width="29.83203125" customWidth="1"/>
-    <col min="13" max="13" width="29.83203125" customWidth="1"/>
-    <col min="14" max="14" width="20.83203125" customWidth="1"/>
-    <col min="15" max="15" width="12.83203125" customWidth="1"/>
+    <col width="18.83203125" customWidth="1" min="1" max="1"/>
+    <col width="24.83203125" customWidth="1" min="2" max="2"/>
+    <col width="15.83203125" customWidth="1" min="3" max="3"/>
+    <col width="18.83203125" customWidth="1" min="4" max="4"/>
+    <col width="18.83203125" customWidth="1" min="5" max="5"/>
+    <col width="17.83203125" customWidth="1" min="6" max="6"/>
+    <col width="18.83203125" customWidth="1" min="7" max="7"/>
+    <col width="23.83203125" customWidth="1" min="8" max="8"/>
+    <col width="30.83203125" customWidth="1" min="9" max="9"/>
+    <col width="24.83203125" customWidth="1" min="10" max="10"/>
+    <col width="15.83203125" customWidth="1" min="11" max="11"/>
+    <col width="29.83203125" customWidth="1" min="12" max="12"/>
+    <col width="29.83203125" customWidth="1" min="13" max="13"/>
+    <col width="20.83203125" customWidth="1" min="14" max="14"/>
+    <col width="12.83203125" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>project_code</v>
-      </c>
-      <c r="B1" t="str">
-        <v>entity_document_number</v>
-      </c>
-      <c r="C1" t="str">
-        <v>date_received</v>
-      </c>
-      <c r="D1" t="str">
-        <v>title</v>
-      </c>
-      <c r="E1" t="str">
-        <v>quantity</v>
-      </c>
-      <c r="F1" t="str">
-        <v>unit_of_measure</v>
-      </c>
-      <c r="G1" t="str">
-        <v>unit_price</v>
-      </c>
-      <c r="H1" t="str">
-        <v>subtotal</v>
-      </c>
-      <c r="I1" t="str">
-        <v>igv_amount</v>
-      </c>
-      <c r="J1" t="str">
-        <v>total</v>
-      </c>
-      <c r="K1" t="str">
-        <v>currency</v>
-      </c>
-      <c r="L1" t="str">
-        <v>exchange_rate</v>
-      </c>
-      <c r="M1" t="str">
-        <v>status</v>
-      </c>
-      <c r="N1" t="str">
-        <v>document_ref</v>
-      </c>
-      <c r="O1" t="str">
-        <v>notes</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>project_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>entity_document_number</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>date_received</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>unit_of_measure</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>unit_price</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>subtotal</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>igv_amount</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>exchange_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>document_ref</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Project code</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Supplier RUC/DNI</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Date received</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Quote title</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Quantity</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Unit of measure</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Unit price</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Subtotal (before IGV)</v>
-      </c>
-      <c r="I2" t="str">
-        <v>IGV amount (18% of subtotal)</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Total (subtotal + IGV)</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Currency code</v>
-      </c>
-      <c r="L2" t="str">
-        <v>Exchange rate (PEN per USD)</v>
-      </c>
-      <c r="M2" t="str">
-        <v>Quote status</v>
-      </c>
-      <c r="N2" t="str">
-        <v>Document reference</v>
-      </c>
-      <c r="O2" t="str">
-        <v>Notes</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Project code</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Supplier RUC/DNI</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Date received</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Quote title</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Unit of measure</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Unit price</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Subtotal (before IGV)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>IGV amount (18% of subtotal)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Total (subtotal + IGV)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Currency code</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Exchange rate (PEN per USD)</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Quote status</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Document reference</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>PRY001</v>
-      </c>
-      <c r="B3" t="str">
-        <v>20123456789</v>
-      </c>
-      <c r="C3" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Cement supply Q1</v>
-      </c>
-      <c r="E3" t="str">
-        <v>100</v>
-      </c>
-      <c r="F3" t="str">
-        <v>bags</v>
-      </c>
-      <c r="G3" t="str">
-        <v>25.50</v>
-      </c>
-      <c r="H3" t="str">
-        <v>2550.00</v>
-      </c>
-      <c r="I3" t="str">
-        <v>459.00</v>
-      </c>
-      <c r="J3" t="str">
-        <v>3009.00</v>
-      </c>
-      <c r="K3" t="str">
-        <v>PEN</v>
-      </c>
-      <c r="L3" t="str">
-        <v>3.72</v>
-      </c>
-      <c r="M3" t="str">
-        <v>pending</v>
-      </c>
-      <c r="N3" t="str">
-        <v>COT-001</v>
-      </c>
-      <c r="O3" t="str">
-        <v/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PRY001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20123456789</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Cement supply Q1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>bags</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>25.50</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2550.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>459.00</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3009.00</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>COT-001</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>Must exist in DB</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Must exist in DB</v>
-      </c>
-      <c r="C4" t="str">
-        <v>YYYY-MM-DD</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Required</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Optional, number</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Optional</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Optional, number</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Required, number</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Optional, number</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Required, number</v>
-      </c>
-      <c r="K4" t="str">
-        <v>USD, PEN</v>
-      </c>
-      <c r="L4" t="str">
-        <v>Required, 2.5–6.0</v>
-      </c>
-      <c r="M4" t="str">
-        <v>pending, accepted, rejected</v>
-      </c>
-      <c r="N4" t="str">
-        <v>Optional</v>
-      </c>
-      <c r="O4" t="str">
-        <v>Optional</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Must exist in DB</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Must exist in DB</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Optional, number</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Optional, number</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Required, number</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Optional, number</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Required, number</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>USD, PEN</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Required, 2.5–6.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>pending, accepted, rejected</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O4"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/website/public/templates/quotes-template.xlsx
+++ b/website/public/templates/quotes-template.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="44.83203125" customWidth="1"/>
@@ -452,27 +452,27 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>project_code</v>
+        <v>partner_name</v>
       </c>
       <c r="B9" t="str">
         <v>Yes</v>
       </c>
       <c r="C9" t="str">
-        <v>Project code</v>
+        <v>Partner name</v>
       </c>
       <c r="D9" t="str">
-        <v>Must exist in DB</v>
+        <v>Must exist in DB (tagged partner)</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>entity_document_number</v>
+        <v>project_code</v>
       </c>
       <c r="B10" t="str">
         <v>Yes</v>
       </c>
       <c r="C10" t="str">
-        <v>Supplier RUC/DNI</v>
+        <v>Project code</v>
       </c>
       <c r="D10" t="str">
         <v>Must exist in DB</v>
@@ -480,69 +480,69 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>date_received</v>
+        <v>entity_document_number</v>
       </c>
       <c r="B11" t="str">
         <v>Yes</v>
       </c>
       <c r="C11" t="str">
-        <v>Date received</v>
+        <v>Supplier RUC/DNI</v>
       </c>
       <c r="D11" t="str">
-        <v>YYYY-MM-DD</v>
+        <v>Must exist in DB</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>title</v>
+        <v>date_received</v>
       </c>
       <c r="B12" t="str">
         <v>Yes</v>
       </c>
       <c r="C12" t="str">
-        <v>Quote title</v>
+        <v>Date received (quote date)</v>
       </c>
       <c r="D12" t="str">
-        <v/>
+        <v>YYYY-MM-DD</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>quantity</v>
+        <v>title</v>
       </c>
       <c r="B13" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="C13" t="str">
-        <v>Quantity</v>
+        <v>Item title</v>
       </c>
       <c r="D13" t="str">
-        <v>Number</v>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>unit_of_measure</v>
+        <v>category</v>
       </c>
       <c r="B14" t="str">
         <v>No</v>
       </c>
       <c r="C14" t="str">
-        <v>Unit of measure</v>
+        <v>Item category</v>
       </c>
       <c r="D14" t="str">
-        <v/>
+        <v>Must exist in categories</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>unit_price</v>
+        <v>quantity</v>
       </c>
       <c r="B15" t="str">
         <v>No</v>
       </c>
       <c r="C15" t="str">
-        <v>Unit price</v>
+        <v>Quantity</v>
       </c>
       <c r="D15" t="str">
         <v>Number</v>
@@ -550,41 +550,41 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>subtotal</v>
+        <v>unit_of_measure</v>
       </c>
       <c r="B16" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="C16" t="str">
-        <v>Subtotal (before IGV)</v>
+        <v>Unit of measure</v>
       </c>
       <c r="D16" t="str">
-        <v>Number, &gt; 0</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>igv_amount</v>
+        <v>unit_price</v>
       </c>
       <c r="B17" t="str">
         <v>No</v>
       </c>
       <c r="C17" t="str">
-        <v>IGV amount (18% of subtotal)</v>
+        <v>Unit price</v>
       </c>
       <c r="D17" t="str">
-        <v>Number (auto-calculated if blank)</v>
+        <v>Number</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>total</v>
+        <v>subtotal</v>
       </c>
       <c r="B18" t="str">
         <v>Yes</v>
       </c>
       <c r="C18" t="str">
-        <v>Total (subtotal + IGV)</v>
+        <v>Subtotal (before IGV)</v>
       </c>
       <c r="D18" t="str">
         <v>Number, &gt; 0</v>
@@ -667,27 +667,32 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v xml:space="preserve">  - project_code and entity_document_number must already exist in the database</v>
+        <v xml:space="preserve">  - Each row creates a pending invoice (comprobante_type=pending) + one invoice_item</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v xml:space="preserve">  - If quantity and unit_price are provided: subtotal must equal quantity × unit_price</v>
+        <v xml:space="preserve">  - partner_name must match an entity tagged as "partner" in the database</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v xml:space="preserve">  - igv_amount must equal subtotal × 18% (auto-calculated if left blank)</v>
+        <v xml:space="preserve">  - project_code and entity_document_number must already exist in the database</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v xml:space="preserve">  - total must equal subtotal + igv_amount</v>
+        <v xml:space="preserve">  - If quantity and unit_price are provided: subtotal must equal quantity × unit_price</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v xml:space="preserve">  - igv_amount and total are derived automatically (18% IGV)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D30"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -696,16 +701,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O4"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="24.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="17.83203125" customWidth="1"/>
+    <col min="1" max="1" width="35.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="24.83203125" customWidth="1"/>
+    <col min="4" max="4" width="28.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="26.83203125" customWidth="1"/>
     <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="23.83203125" customWidth="1"/>
-    <col min="9" max="9" width="35.83203125" customWidth="1"/>
-    <col min="10" max="10" width="24.83203125" customWidth="1"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="23.83203125" customWidth="1"/>
     <col min="11" max="11" width="15.83203125" customWidth="1"/>
     <col min="12" max="12" width="29.83203125" customWidth="1"/>
     <col min="13" max="13" width="29.83203125" customWidth="1"/>
@@ -715,34 +720,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>partner_name</v>
+      </c>
+      <c r="B1" t="str">
         <v>project_code</v>
       </c>
-      <c r="B1" t="str">
+      <c r="C1" t="str">
         <v>entity_document_number</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>date_received</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>title</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>category</v>
+      </c>
+      <c r="G1" t="str">
         <v>quantity</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>unit_of_measure</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>unit_price</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>subtotal</v>
-      </c>
-      <c r="I1" t="str">
-        <v>igv_amount</v>
-      </c>
-      <c r="J1" t="str">
-        <v>total</v>
       </c>
       <c r="K1" t="str">
         <v>currency</v>
@@ -762,34 +767,34 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>Partner name</v>
+      </c>
+      <c r="B2" t="str">
         <v>Project code</v>
       </c>
-      <c r="B2" t="str">
+      <c r="C2" t="str">
         <v>Supplier RUC/DNI</v>
       </c>
-      <c r="C2" t="str">
-        <v>Date received</v>
-      </c>
       <c r="D2" t="str">
-        <v>Quote title</v>
+        <v>Date received (quote date)</v>
       </c>
       <c r="E2" t="str">
+        <v>Item title</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Item category</v>
+      </c>
+      <c r="G2" t="str">
         <v>Quantity</v>
       </c>
-      <c r="F2" t="str">
+      <c r="H2" t="str">
         <v>Unit of measure</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>Unit price</v>
       </c>
-      <c r="H2" t="str">
+      <c r="J2" t="str">
         <v>Subtotal (before IGV)</v>
-      </c>
-      <c r="I2" t="str">
-        <v>IGV amount (18% of subtotal)</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Total (subtotal + IGV)</v>
       </c>
       <c r="K2" t="str">
         <v>Currency code</v>
@@ -809,34 +814,34 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>Korakuen SAC</v>
+      </c>
+      <c r="B3" t="str">
         <v>PRY001</v>
       </c>
-      <c r="B3" t="str">
+      <c r="C3" t="str">
         <v>20123456789</v>
       </c>
-      <c r="C3" t="str">
+      <c r="D3" t="str">
         <v>2026-03-15</v>
       </c>
-      <c r="D3" t="str">
+      <c r="E3" t="str">
         <v>Cement supply Q1</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
+        <v>materials</v>
+      </c>
+      <c r="G3" t="str">
         <v>100</v>
       </c>
-      <c r="F3" t="str">
+      <c r="H3" t="str">
         <v>bags</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>25.50</v>
       </c>
-      <c r="H3" t="str">
+      <c r="J3" t="str">
         <v>2550.00</v>
-      </c>
-      <c r="I3" t="str">
-        <v>459.00</v>
-      </c>
-      <c r="J3" t="str">
-        <v>3009.00</v>
       </c>
       <c r="K3" t="str">
         <v>PEN</v>
@@ -856,31 +861,31 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Must exist in DB</v>
+        <v>Must exist in DB (tagged partner)</v>
       </c>
       <c r="B4" t="str">
         <v>Must exist in DB</v>
       </c>
       <c r="C4" t="str">
+        <v>Must exist in DB</v>
+      </c>
+      <c r="D4" t="str">
         <v>YYYY-MM-DD</v>
       </c>
-      <c r="D4" t="str">
+      <c r="E4" t="str">
         <v/>
       </c>
-      <c r="E4" t="str">
-        <v>Number</v>
-      </c>
       <c r="F4" t="str">
-        <v/>
+        <v>Must exist in categories</v>
       </c>
       <c r="G4" t="str">
         <v>Number</v>
       </c>
       <c r="H4" t="str">
-        <v>Number, &gt; 0</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>Number (auto-calculated if blank)</v>
+        <v>Number</v>
       </c>
       <c r="J4" t="str">
         <v>Number, &gt; 0</v>

--- a/website/public/templates/quotes-template.xlsx
+++ b/website/public/templates/quotes-template.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D33"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="44.83203125" customWidth="1"/>
@@ -667,32 +667,47 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v xml:space="preserve">  - Each row creates a pending invoice (comprobante_type=pending) + one invoice_item</v>
+        <v xml:space="preserve">  - Each row creates a quote (pending invoice) + one invoice_item</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v xml:space="preserve">  - partner_name must match an entity tagged as "partner" in the database</v>
+        <v xml:space="preserve">  - Quotes with status "pending" or "rejected" are invisible to financial views</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v xml:space="preserve">  - project_code and entity_document_number must already exist in the database</v>
+        <v xml:space="preserve">  - Only "accepted" quotes become real invoices visible in totals, balances, and settlement</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v xml:space="preserve">  - If quantity and unit_price are provided: subtotal must equal quantity × unit_price</v>
+        <v xml:space="preserve">  - You can change quote status from the Prices page after import</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
+        <v xml:space="preserve">  - partner_name must match an entity tagged as "partner" in the database</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v xml:space="preserve">  - project_code and entity_document_number must already exist in the database</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v xml:space="preserve">  - If quantity and unit_price are provided: subtotal must equal quantity × unit_price</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
         <v xml:space="preserve">  - igv_amount and total are derived automatically (18% IGV)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D33"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/website/public/templates/quotes-template.xlsx
+++ b/website/public/templates/quotes-template.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="44.83203125" customWidth="1"/>
@@ -612,7 +612,7 @@
         <v>Yes</v>
       </c>
       <c r="C20" t="str">
-        <v>Exchange rate (PEN per USD)</v>
+        <v>Exchange rate (PEN per USD). Auto-filled from DB if blank</v>
       </c>
       <c r="D20" t="str">
         <v>2.5–6.0</v>
@@ -637,13 +637,13 @@
         <v>document_ref</v>
       </c>
       <c r="B22" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="C22" t="str">
-        <v>Document reference</v>
+        <v>Quote number (grouping key)</v>
       </c>
       <c r="D22" t="str">
-        <v/>
+        <v>Rows w/ same value → one quote</v>
       </c>
     </row>
     <row r="23">
@@ -667,47 +667,52 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v xml:space="preserve">  - Each row creates a quote (pending invoice) + one invoice_item</v>
+        <v xml:space="preserve">  - Rows with the same document_ref are grouped into ONE quote with multiple line items</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v xml:space="preserve">  - Quotes with status "pending" or "rejected" are invisible to financial views</v>
+        <v xml:space="preserve">  - All grouped rows must share the same partner, project, supplier, date, currency, status, notes</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v xml:space="preserve">  - Only "accepted" quotes become real invoices visible in totals, balances, and settlement</v>
+        <v xml:space="preserve">  - Quotes with status "pending" or "rejected" are invisible to financial views</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v xml:space="preserve">  - You can change quote status from the Prices page after import</v>
+        <v xml:space="preserve">  - Only "accepted" quotes become real invoices visible in totals, balances, and settlement</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v xml:space="preserve">  - partner_name must match an entity tagged as "partner" in the database</v>
+        <v xml:space="preserve">  - You can change quote status from the Prices page after import</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v xml:space="preserve">  - project_code and entity_document_number must already exist in the database</v>
+        <v xml:space="preserve">  - partner_name must match an entity tagged as "partner" in the database</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v xml:space="preserve">  - If quantity and unit_price are provided: subtotal must equal quantity × unit_price</v>
+        <v xml:space="preserve">  - project_code and entity_document_number must already exist in the database</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
+        <v xml:space="preserve">  - If quantity and unit_price are provided: subtotal must equal quantity × unit_price</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
         <v xml:space="preserve">  - igv_amount and total are derived automatically (18% IGV)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D34"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -727,9 +732,9 @@
     <col min="9" max="9" width="12.83203125" customWidth="1"/>
     <col min="10" max="10" width="23.83203125" customWidth="1"/>
     <col min="11" max="11" width="15.83203125" customWidth="1"/>
-    <col min="12" max="12" width="29.83203125" customWidth="1"/>
+    <col min="12" max="12" width="40.83203125" customWidth="1"/>
     <col min="13" max="13" width="29.83203125" customWidth="1"/>
-    <col min="14" max="14" width="20.83203125" customWidth="1"/>
+    <col min="14" max="14" width="32.83203125" customWidth="1"/>
     <col min="15" max="15" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -815,13 +820,13 @@
         <v>Currency code</v>
       </c>
       <c r="L2" t="str">
-        <v>Exchange rate (PEN per USD)</v>
+        <v>Exchange rate (PEN per USD). Auto-filled from DB if blank</v>
       </c>
       <c r="M2" t="str">
         <v>Quote status</v>
       </c>
       <c r="N2" t="str">
-        <v>Document reference</v>
+        <v>Quote number (grouping key)</v>
       </c>
       <c r="O2" t="str">
         <v>Notes</v>
@@ -915,7 +920,7 @@
         <v>pending, accepted, rejected</v>
       </c>
       <c r="N4" t="str">
-        <v/>
+        <v>Rows w/ same value → one quote</v>
       </c>
       <c r="O4" t="str">
         <v/>
